--- a/Result/profitability/2308.xlsx
+++ b/Result/profitability/2308.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM86"/>
+  <dimension ref="A1:AM87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,10 +667,10 @@
         <v>0.84</v>
       </c>
       <c r="M2" t="n">
-        <v>4.925000000000001</v>
+        <v>5.54125</v>
       </c>
       <c r="N2" t="n">
-        <v>32.57875</v>
+        <v>32.6675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -776,10 +776,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4325</v>
+        <v>5.297499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>30.71625</v>
+        <v>31.325</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -893,10 +893,10 @@
         <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>4.23125</v>
+        <v>4.94875</v>
       </c>
       <c r="N4" t="n">
-        <v>29.21125</v>
+        <v>29.69375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1010,10 +1010,10 @@
         <v>1.58</v>
       </c>
       <c r="M5" t="n">
-        <v>3.93625</v>
+        <v>4.475</v>
       </c>
       <c r="N5" t="n">
-        <v>27.74</v>
+        <v>27.75625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>3.44375</v>
+        <v>3.75875</v>
       </c>
       <c r="N6" t="n">
-        <v>26.13125</v>
+        <v>26.2275</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>1.46</v>
       </c>
       <c r="M7" t="n">
-        <v>2.73125</v>
+        <v>3.1075</v>
       </c>
       <c r="N7" t="n">
-        <v>24.52</v>
+        <v>24.65125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>1.74</v>
       </c>
       <c r="M8" t="n">
-        <v>2.115</v>
+        <v>2.33625</v>
       </c>
       <c r="N8" t="n">
-        <v>22.84125</v>
+        <v>22.67125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -11326,6 +11326,133 @@
       </c>
       <c r="AM86" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>183256</v>
+      </c>
+      <c r="D87" t="n">
+        <v>117948</v>
+      </c>
+      <c r="E87" t="n">
+        <v>65308</v>
+      </c>
+      <c r="F87" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="G87" t="n">
+        <v>30570</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>16.68%</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>4430</v>
+      </c>
+      <c r="J87" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K87" t="n">
+        <v>25136</v>
+      </c>
+      <c r="L87" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="M87" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="N87" t="n">
+        <v>34.38625</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
+      </c>
+      <c r="V87" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W87" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0.2237673830594185</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>-1.359999999999999</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>-0.03675675675675671</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0.802607076350093</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0.1300000000000026</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0.003660940580118455</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK87" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
